--- a/sales performance dashboard.xlsx
+++ b/sales performance dashboard.xlsx
@@ -5,10 +5,10 @@
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imad khan\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\imad khan\Downloads\Excel project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{555B44EE-059F-42F1-9597-7D65D64B787A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A520C6F7-76A0-4020-9CF0-08E7FE165F0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,9 +22,9 @@
   <definedNames>
     <definedName name="Slicer_City">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="12" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
@@ -34,6 +34,17 @@
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
       <x14:workbookPr/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -893,13 +904,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -948,7 +958,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Data_Analyst_Excel_Project.xlsx]best city!PivotTable1</c:name>
+    <c:name>[sales performance dashboard.xlsx]best city!PivotTable1</c:name>
     <c:fmtId val="2"/>
   </c:pivotSource>
   <c:chart>
@@ -1100,57 +1110,7 @@
           </a:sp3d>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:shade val="51000"/>
-                    <a:satMod val="130000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="80000">
-                  <a:schemeClr val="accent1">
-                    <a:shade val="93000"/>
-                    <a:satMod val="130000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:shade val="94000"/>
-                    <a:satMod val="135000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="16200000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="35000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-            <a:scene3d>
-              <a:camera prst="orthographicFront">
-                <a:rot lat="0" lon="0" rev="0"/>
-              </a:camera>
-              <a:lightRig rig="threePt" dir="t">
-                <a:rot lat="0" lon="0" rev="1200000"/>
-              </a:lightRig>
-            </a:scene3d>
-            <a:sp3d>
-              <a:bevelT w="63500" h="25400"/>
-            </a:sp3d>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -1583,7 +1543,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Data_Analyst_Excel_Project.xlsx]bes sales man!PivotTable2</c:name>
+    <c:name>[sales performance dashboard.xlsx]bes sales man!PivotTable2</c:name>
     <c:fmtId val="2"/>
   </c:pivotSource>
   <c:chart>
@@ -1593,12 +1553,26 @@
           <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
           <a:lstStyle/>
           <a:p>
-            <a:pPr>
+            <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+              <a:lnSpc>
+                <a:spcPct val="100000"/>
+              </a:lnSpc>
+              <a:spcBef>
+                <a:spcPts val="0"/>
+              </a:spcBef>
+              <a:spcAft>
+                <a:spcPts val="0"/>
+              </a:spcAft>
+              <a:buClrTx/>
+              <a:buSzTx/>
+              <a:buFontTx/>
+              <a:buNone/>
+              <a:tabLst/>
               <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
                 <a:solidFill>
-                  <a:schemeClr val="lt1">
+                  <a:sysClr val="window" lastClr="FFFFFF">
                     <a:lumMod val="95000"/>
-                  </a:schemeClr>
+                  </a:sysClr>
                 </a:solidFill>
                 <a:effectLst>
                   <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
@@ -1613,8 +1587,21 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Sales by Product</a:t>
+              <a:rPr lang="en-US" sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
+                <a:solidFill>
+                  <a:sysClr val="window" lastClr="FFFFFF">
+                    <a:lumMod val="95000"/>
+                  </a:sysClr>
+                </a:solidFill>
+                <a:effectLst>
+                  <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
+                    <a:prstClr val="black">
+                      <a:alpha val="40000"/>
+                    </a:prstClr>
+                  </a:outerShdw>
+                </a:effectLst>
+              </a:rPr>
+              <a:t>Sales by Salesperson</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1631,12 +1618,26 @@
         <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr>
+          <a:pPr marL="0" marR="0" lvl="0" indent="0" algn="ctr" defTabSz="914400" rtl="0" eaLnBrk="1" fontAlgn="auto" latinLnBrk="0" hangingPunct="1">
+            <a:lnSpc>
+              <a:spcPct val="100000"/>
+            </a:lnSpc>
+            <a:spcBef>
+              <a:spcPts val="0"/>
+            </a:spcBef>
+            <a:spcAft>
+              <a:spcPts val="0"/>
+            </a:spcAft>
+            <a:buClrTx/>
+            <a:buSzTx/>
+            <a:buFontTx/>
+            <a:buNone/>
+            <a:tabLst/>
             <a:defRPr sz="1600" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="100" baseline="0">
               <a:solidFill>
-                <a:schemeClr val="lt1">
+                <a:sysClr val="window" lastClr="FFFFFF">
                   <a:lumMod val="95000"/>
-                </a:schemeClr>
+                </a:sysClr>
               </a:solidFill>
               <a:effectLst>
                 <a:outerShdw blurRad="50800" dist="38100" dir="5400000" algn="t" rotWithShape="0">
@@ -1735,57 +1736,7 @@
           </a:sp3d>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:shade val="51000"/>
-                    <a:satMod val="130000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="80000">
-                  <a:schemeClr val="accent1">
-                    <a:shade val="93000"/>
-                    <a:satMod val="130000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:shade val="94000"/>
-                    <a:satMod val="135000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="16200000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="35000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-            <a:scene3d>
-              <a:camera prst="orthographicFront">
-                <a:rot lat="0" lon="0" rev="0"/>
-              </a:camera>
-              <a:lightRig rig="threePt" dir="t">
-                <a:rot lat="0" lon="0" rev="1200000"/>
-              </a:lightRig>
-            </a:scene3d>
-            <a:sp3d>
-              <a:bevelT w="63500" h="25400"/>
-            </a:sp3d>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -2224,7 +2175,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Data_Analyst_Excel_Project.xlsx]best product!PivotTable4</c:name>
+    <c:name>[sales performance dashboard.xlsx]best product!PivotTable4</c:name>
     <c:fmtId val="2"/>
   </c:pivotSource>
   <c:chart>
@@ -2255,7 +2206,11 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Sales by Salesperson</a:t>
+              <a:t>Sales by</a:t>
+            </a:r>
+            <a:r>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> product</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -2376,57 +2331,7 @@
           </a:sp3d>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="6"/>
-          <c:spPr>
-            <a:gradFill rotWithShape="1">
-              <a:gsLst>
-                <a:gs pos="0">
-                  <a:schemeClr val="accent1">
-                    <a:shade val="51000"/>
-                    <a:satMod val="130000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="80000">
-                  <a:schemeClr val="accent1">
-                    <a:shade val="93000"/>
-                    <a:satMod val="130000"/>
-                  </a:schemeClr>
-                </a:gs>
-                <a:gs pos="100000">
-                  <a:schemeClr val="accent1">
-                    <a:shade val="94000"/>
-                    <a:satMod val="135000"/>
-                  </a:schemeClr>
-                </a:gs>
-              </a:gsLst>
-              <a:lin ang="16200000" scaled="0"/>
-            </a:gradFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst>
-              <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-                <a:srgbClr val="000000">
-                  <a:alpha val="35000"/>
-                </a:srgbClr>
-              </a:outerShdw>
-            </a:effectLst>
-            <a:scene3d>
-              <a:camera prst="orthographicFront">
-                <a:rot lat="0" lon="0" rev="0"/>
-              </a:camera>
-              <a:lightRig rig="threePt" dir="t">
-                <a:rot lat="0" lon="0" rev="1200000"/>
-              </a:lightRig>
-            </a:scene3d>
-            <a:sp3d>
-              <a:bevelT w="63500" h="25400"/>
-            </a:sp3d>
-          </c:spPr>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
@@ -4534,8 +4439,8 @@
       <xdr:row>20</xdr:row>
       <xdr:rowOff>28574</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+      <mc:Choice Requires="a14">
         <xdr:graphicFrame macro="">
           <xdr:nvGraphicFramePr>
             <xdr:cNvPr id="6" name="City">
@@ -4558,7 +4463,7 @@
           </a:graphic>
         </xdr:graphicFrame>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
             <xdr:cNvPr id="0" name=""/>
@@ -5871,7 +5776,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{33B83BC8-EC0B-42F3-A2B2-385EFB8806BA}" name="PivotTable1" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{33B83BC8-EC0B-42F3-A2B2-385EFB8806BA}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="8">
   <location ref="A3:B8" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -5962,7 +5867,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A204D9C0-0FB8-42A4-B267-F2E87530D85C}" name="PivotTable2" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{A204D9C0-0FB8-42A4-B267-F2E87530D85C}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="5">
   <location ref="A3:B9" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -6046,7 +5951,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{35F0DF70-2886-41A3-A436-DC78149D7795}" name="PivotTable4" cacheId="12" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{35F0DF70-2886-41A3-A436-DC78149D7795}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" chartFormat="4">
   <location ref="A3:B10" firstHeaderRow="1" firstDataRow="1" firstDataCol="1"/>
   <pivotFields count="10">
     <pivotField showAll="0"/>
@@ -6463,7 +6368,7 @@
       <c r="A4" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <v>18140</v>
       </c>
     </row>
@@ -6471,7 +6376,7 @@
       <c r="A5" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>16980</v>
       </c>
     </row>
@@ -6479,7 +6384,7 @@
       <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <v>48610</v>
       </c>
     </row>
@@ -6487,7 +6392,7 @@
       <c r="A7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7">
         <v>19455</v>
       </c>
     </row>
@@ -6495,7 +6400,7 @@
       <c r="A8" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8">
         <v>103185</v>
       </c>
     </row>
@@ -6522,64 +6427,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="46" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>243</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>245</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="I1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>252</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="26" x14ac:dyDescent="0.35">
-      <c r="A2" s="8">
+      <c r="A2" s="7">
         <v>103185</v>
       </c>
-      <c r="B2" s="9" t="s">
+      <c r="B2" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="8" t="s">
         <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="4"/>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
     </row>
     <row r="24" spans="9:9" ht="21" x14ac:dyDescent="0.5">
-      <c r="I24" s="6" t="s">
+      <c r="I24" s="5" t="s">
         <v>247</v>
       </c>
     </row>
     <row r="25" spans="9:9" ht="21" x14ac:dyDescent="0.5">
-      <c r="I25" s="5" t="s">
+      <c r="I25" s="4" t="s">
         <v>248</v>
       </c>
     </row>
     <row r="26" spans="9:9" ht="21" x14ac:dyDescent="0.5">
-      <c r="I26" s="5" t="s">
+      <c r="I26" s="4" t="s">
         <v>249</v>
       </c>
     </row>
     <row r="27" spans="9:9" ht="21" x14ac:dyDescent="0.5">
-      <c r="I27" s="5" t="s">
+      <c r="I27" s="4" t="s">
         <v>250</v>
       </c>
     </row>
     <row r="28" spans="9:9" ht="21" x14ac:dyDescent="0.5">
-      <c r="I28" s="5" t="s">
+      <c r="I28" s="4" t="s">
         <v>251</v>
       </c>
     </row>
@@ -6617,7 +6522,7 @@
       <c r="A4" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <v>27205</v>
       </c>
     </row>
@@ -6625,7 +6530,7 @@
       <c r="A5" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>32945</v>
       </c>
     </row>
@@ -6633,7 +6538,7 @@
       <c r="A6" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <v>9095</v>
       </c>
     </row>
@@ -6641,7 +6546,7 @@
       <c r="A7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7">
         <v>18550</v>
       </c>
     </row>
@@ -6649,7 +6554,7 @@
       <c r="A8" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8">
         <v>15390</v>
       </c>
     </row>
@@ -6657,7 +6562,7 @@
       <c r="A9" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9">
         <v>103185</v>
       </c>
     </row>
@@ -6687,7 +6592,7 @@
       <c r="A4" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B4" s="3">
+      <c r="B4">
         <v>7680</v>
       </c>
     </row>
@@ -6695,7 +6600,7 @@
       <c r="A5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="B5" s="3">
+      <c r="B5">
         <v>3675</v>
       </c>
     </row>
@@ -6703,7 +6608,7 @@
       <c r="A6" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="B6" s="3">
+      <c r="B6">
         <v>60000</v>
       </c>
     </row>
@@ -6711,7 +6616,7 @@
       <c r="A7" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="3">
+      <c r="B7">
         <v>16200</v>
       </c>
     </row>
@@ -6719,7 +6624,7 @@
       <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="3">
+      <c r="B8">
         <v>1980</v>
       </c>
     </row>
@@ -6727,7 +6632,7 @@
       <c r="A9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="3">
+      <c r="B9">
         <v>13650</v>
       </c>
     </row>
@@ -6735,7 +6640,7 @@
       <c r="A10" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="B10" s="3">
+      <c r="B10">
         <v>103185</v>
       </c>
     </row>
